--- a/docentes/Bautista Sarao Eutiquio - Estadisticos 20211.xlsx
+++ b/docentes/Bautista Sarao Eutiquio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -85,25 +85,73 @@
     <t>BAEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
     <t>COBOS</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
   </si>
   <si>
     <t>TAMAYO</t>
   </si>
   <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>FRIAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>NOLASCO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>VARGAS</t>
@@ -112,19 +160,52 @@
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>YOLET</t>
   </si>
   <si>
-    <t>YAIR</t>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>JOSMAR JAHIR</t>
   </si>
   <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
     <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -974,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1012,10 +1093,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1024,21 +1105,21 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920007</v>
+        <v>21330051920009</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1047,21 +1128,21 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920017</v>
+        <v>21330051920013</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1070,21 +1151,21 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920025</v>
+        <v>21330051920017</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1093,30 +1174,260 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920045</v>
+        <v>21330051920026</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920037</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920070</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920007</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920019</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920016</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920023</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920025</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920032</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920045</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920392</v>
+      </c>
+      <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Bautista Sarao Eutiquio - Estadisticos 20211.xlsx
+++ b/docentes/Bautista Sarao Eutiquio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -91,9 +91,6 @@
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -106,36 +103,21 @@
     <t>COBOS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
     <t>TAMAYO</t>
   </si>
   <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
     <t>FRIAS</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -148,21 +130,12 @@
     <t>NOLASCO</t>
   </si>
   <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>VARGAS</t>
   </si>
   <si>
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
@@ -172,9 +145,6 @@
     <t>OMAR</t>
   </si>
   <si>
-    <t>YAIR</t>
-  </si>
-  <si>
     <t>OSVALDO</t>
   </si>
   <si>
@@ -187,25 +157,13 @@
     <t>YOLET</t>
   </si>
   <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
     <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>JOSMAR JAHIR</t>
   </si>
   <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
     <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -606,19 +564,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,19 +590,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -658,19 +616,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H4">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -684,19 +642,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -710,19 +668,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>78.26000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -775,16 +733,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>37.5</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -798,16 +759,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>56.82</v>
+      </c>
+      <c r="H3">
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,16 +785,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>57.14</v>
+      </c>
+      <c r="H4">
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -844,16 +811,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
         <v>18</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.26000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -867,16 +837,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>69.56999999999999</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -929,19 +902,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -955,19 +928,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -981,19 +954,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H4">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1007,19 +980,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1033,19 +1006,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>78.26000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1093,10 +1066,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1116,10 +1089,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1139,10 +1112,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1156,16 +1129,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920017</v>
+        <v>21330051920026</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1179,22 +1152,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920026</v>
+        <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1202,16 +1175,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920037</v>
+        <v>21330051920070</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1225,39 +1198,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920070</v>
+        <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920007</v>
+        <v>21330051920023</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1271,16 +1244,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920019</v>
+        <v>21330051920025</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1294,140 +1267,25 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920016</v>
+        <v>21330051920045</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920023</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920025</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920032</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920045</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
         <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920392</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Bautista Sarao Eutiquio - Estadisticos 20211.xlsx
+++ b/docentes/Bautista Sarao Eutiquio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,90 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>FRIAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
   </si>
 </sst>
 </file>
@@ -564,19 +480,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -590,19 +506,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -616,19 +532,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -642,19 +558,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>86.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -668,19 +584,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -733,19 +649,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -759,19 +675,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>56.82</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -785,19 +701,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>57.14</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -811,19 +727,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>78.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -837,19 +753,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>69.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -902,19 +818,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -928,19 +844,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -954,19 +870,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -980,19 +896,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>86.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1006,19 +922,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1058,236 +974,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920003</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920009</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920013</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920026</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920037</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920070</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920023</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920025</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920045</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
